--- a/output/pdf_financials_xlsx/VZZ.xlsx
+++ b/output/pdf_financials_xlsx/VZZ.xlsx
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.606892</v>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -32302,13 +32302,13 @@
         </is>
       </c>
       <c r="E373" s="5" t="n">
-        <v>0.09263100000000001</v>
+        <v>-0.09263100000000001</v>
       </c>
       <c r="F373" s="5" t="n">
-        <v>1.521253</v>
+        <v>-1.521253</v>
       </c>
       <c r="G373" s="5" t="n">
-        <v>0.273501</v>
+        <v>-0.273501</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VZZ.xlsx
+++ b/output/pdf_financials_xlsx/VZZ.xlsx
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000174</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00042</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.09263100000000001</v>
+        <v>-0.092457</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.521253</v>
+        <v>-1.520833</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.273501</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.09263100000000001</v>
+        <v>-0.092457</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.521253</v>
+        <v>-1.520833</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.273501</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.07057099999999999</v>
+        <v>0.011846</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.355967</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.07057099999999999</v>
+        <v>0.011846</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.355967</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.001636</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.019339</v>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -32014,7 +32014,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" s="5" t="n">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" s="5" t="n">

--- a/output/pdf_financials_xlsx/VZZ.xlsx
+++ b/output/pdf_financials_xlsx/VZZ.xlsx
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.002008</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.001646</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.000708</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.000708</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -3774,16 +3774,16 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.002008</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.001646</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.000708</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.000708</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -3942,16 +3942,16 @@
         <v>0.002885</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.002008</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.148656</v>
+        <v>0.14701</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.092835</v>
+        <v>0.092127</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.101682</v>
+        <v>0.100974</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -4166,20 +4166,16 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.002244472177500024</v>
+        <v>0.00415741790433366</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.0003314156785829639</v>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001101910321164261</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.0002333514609185742</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.0002660413942372728</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -12137,7 +12133,11 @@
           <t>Lease liabilities -</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -14140,7 +14140,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -17606,7 +17610,11 @@
           <t>Lease liabilities 4</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -23661,7 +23669,11 @@
           <t>Proceeds from issuance of units under private placement 13</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -25907,7 +25919,11 @@
           <t>Proceeds from issuance of units under a private placement 14</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -27104,7 +27120,11 @@
           <t>Proceeds from issuance of units under a private placement 13</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -28145,7 +28165,11 @@
           <t>Proceeds from issuance of units under a private placement 12</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -28849,7 +28873,11 @@
           <t>Issuance of shares under a private placement</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -29283,7 +29311,11 @@
           <t>Issuance of units under a private placement</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -30334,7 +30366,11 @@
           <t>Issuance of units under a private placement 7</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
